--- a/reports/二级子公司D_利润表_2025-03.xlsx
+++ b/reports/二级子公司D_利润表_2025-03.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>82715179</v>
+        <v>84714050</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>80869726</v>
+        <v>81060171</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>223784848</v>
+        <v>223242477</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>279438</v>
+        <v>281635</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>772258</v>
+        <v>774621</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>240905</v>
+        <v>241414</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>663290</v>
+        <v>664906</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>198979</v>
+        <v>200981</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>550987</v>
+        <v>554506</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>181055</v>
+        <v>180550</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>497852</v>
+        <v>499036</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>99404</v>
+        <v>100067</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>275403</v>
+        <v>277013</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>80430</v>
+        <v>79853</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>221233</v>
+        <v>221284</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>81634968</v>
+        <v>83629550</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>79789515</v>
+        <v>79975671</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4497399</v>
+        <v>4473001</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>12417050</v>
+        <v>12379839</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>349498</v>
+        <v>348092</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>965524</v>
+        <v>961842</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>601971</v>
+        <v>597633</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>1657932</v>
+        <v>1648351</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>71656978</v>
+        <v>71874490</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>198380491</v>
+        <v>197901323</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1206845</v>
+        <v>1200918</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>3318814</v>
+        <v>3302409</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>397601</v>
+        <v>401255</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1101601</v>
+        <v>1102716</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2011229</v>
+        <v>2009920</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>5531281</v>
+        <v>5524283</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>497703</v>
+        <v>502954</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1377679</v>
+        <v>1383556</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1805500</v>
+        <v>1810471</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>4973619</v>
+        <v>4987501</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>39953</v>
+        <v>40188</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>119949</v>
+        <v>120549</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1082981</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>2994016</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>720239</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>1994163</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>54245466</v>
+        <v>58128750</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>48618080</v>
+        <v>48624896</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>47712862</v>
+        <v>47730285</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>132193234</v>
+        <v>132236924</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>905218</v>
+        <v>894611</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>2489235</v>
+        <v>2475519</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1790456</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>4946176</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>573878</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>1582449</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>359490</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>989631</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>432474</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1189114</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>325108</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>893427</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>217111</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>596775</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>181072</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>498186</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>844980</v>
+        <v>854866</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>2340993</v>
+        <v>2355516</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>653850</v>
+        <v>652915</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>1797857</v>
+        <v>1802270</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>497365</v>
+        <v>501228</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>1377347</v>
+        <v>1386006</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3815276</v>
+        <v>3799979</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>10503491</v>
+        <v>10522913</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>149653</v>
+        <v>149630</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>449641</v>
+        <v>414711</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>320112</v>
+        <v>318562</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>960140</v>
+        <v>960002</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>360596</v>
+        <v>318562</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1080565</v>
+        <v>960002</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>39861</v>
+        <v>39762</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>119864</v>
+        <v>119584</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>161168</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>483843</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>313925</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>865432</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>107883</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>322710</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>81116</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>242356</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>135499</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>404656</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>452388</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1243593</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>72431</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>216616</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>54303</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>162665</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>90383</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>271253</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>63135</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>189823</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>44985</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>135446</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>108180</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>26873</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>80979</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>27389502</v>
+        <v>26609488</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31462756</v>
+        <v>29556290</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>179108</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>494551</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>44859</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>134382</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>69830</v>
+        <v>69947</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>209836</v>
+        <v>209193</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>27319672</v>
+        <v>26718649</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2486675</v>
+        <v>2509882</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>7486781</v>
+        <v>7495564</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24832997</v>
+        <v>24208767</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24832997</v>
+        <v>24208767</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24832997</v>
+        <v>24208767</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24832997</v>
+        <v>24208767</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24832997</v>
+        <v>24208767</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
